--- a/idecba/supermercados.xlsx
+++ b/idecba/supermercados.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\SRV03\Centro_Doc\BANCO DE DATOS\CARPETAS BCO DE DATOS\COMERCIO INTERIOR\SUPERMERCADOS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\SRV03\Centro_Doc\BANCO DE DATOS\CARPETAS BCO DE DATOS\COMERCIO INTERIOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="10830"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21060" windowHeight="8865"/>
   </bookViews>
   <sheets>
     <sheet name="AC_S_01" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="66">
   <si>
     <t>Período</t>
   </si>
@@ -254,7 +254,7 @@
     <t>2025*</t>
   </si>
   <si>
-    <t>Ventas a valores constantes en supermercados. Variación interanual (%). Ciudad de Buenos Aires. Años 2001/junio de 2026</t>
+    <t>Ventas a valores constantes en supermercados. Variación interanual (%). Ciudad de Buenos Aires. Años 2001/julio de 2026</t>
   </si>
 </sst>
 </file>
@@ -1445,7 +1445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J208"/>
+  <dimension ref="A1:J209"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.5703125" style="21" customWidth="1"/>
@@ -3605,7 +3605,7 @@
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A179" s="21" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="B179" s="30">
         <v>-6.7544675951070161</v>
@@ -3885,46 +3885,57 @@
         <v>-2.2404135904803057</v>
       </c>
     </row>
-    <row r="205" spans="1:10" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A205" s="36" t="s">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A205" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B205" s="30">
+        <v>0.72747850812768799</v>
+      </c>
+      <c r="C205" s="30">
+        <v>0.74044303817519808</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A206" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="B205" s="36"/>
-      <c r="C205" s="36"/>
-    </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A206" s="37" t="s">
+      <c r="B206" s="36"/>
+      <c r="C206" s="36"/>
+    </row>
+    <row r="207" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A207" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="B206" s="37"/>
-      <c r="C206" s="37"/>
-      <c r="D206" s="29"/>
-      <c r="E206" s="29"/>
-      <c r="F206" s="29"/>
-      <c r="H206" s="29"/>
-      <c r="I206" s="29"/>
-      <c r="J206" s="29"/>
-    </row>
-    <row r="207" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A207" s="35" t="s">
+      <c r="B207" s="37"/>
+      <c r="C207" s="37"/>
+      <c r="D207" s="29"/>
+      <c r="E207" s="29"/>
+      <c r="F207" s="29"/>
+      <c r="H207" s="29"/>
+      <c r="I207" s="29"/>
+      <c r="J207" s="29"/>
+    </row>
+    <row r="208" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A208" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="B207" s="35"/>
-      <c r="C207" s="35"/>
-    </row>
-    <row r="208" spans="1:10" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A208" s="34" t="s">
+      <c r="B208" s="35"/>
+      <c r="C208" s="35"/>
+    </row>
+    <row r="209" spans="1:3" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A209" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="B208" s="34"/>
-      <c r="C208" s="34"/>
+      <c r="B209" s="34"/>
+      <c r="C209" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A209:C209"/>
     <mergeCell ref="A208:C208"/>
+    <mergeCell ref="A206:C206"/>
     <mergeCell ref="A207:C207"/>
-    <mergeCell ref="A205:C205"/>
-    <mergeCell ref="A206:C206"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:C2"/>
@@ -3995,7 +4006,7 @@
       </c>
       <c r="D6" s="10"/>
     </row>
-    <row r="7" spans="1:4" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>40</v>
       </c>
@@ -4011,7 +4022,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>42</v>
       </c>
@@ -4028,7 +4039,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
         <v>44</v>
       </c>
@@ -4036,7 +4047,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>45</v>
       </c>
@@ -4044,7 +4055,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>46</v>
       </c>
@@ -4052,7 +4063,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>47</v>
       </c>

--- a/idecba/supermercados.xlsx
+++ b/idecba/supermercados.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\SRV03\Centro_Doc\BANCO DE DATOS\CARPETAS BCO DE DATOS\COMERCIO INTERIOR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.32.3.50\Centro_Doc\BANCO DE DATOS\CARPETAS BCO DE DATOS\COMERCIO INTERIOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EE5A4DC-C24C-41AB-BE99-C7FB8234573F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21060" windowHeight="8865"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AC_S_01" sheetId="1" r:id="rId1"/>
@@ -19,24 +20,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Ficha Técnica'!$A:$B</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="66">
   <si>
     <t>Período</t>
   </si>
@@ -254,13 +242,13 @@
     <t>2025*</t>
   </si>
   <si>
-    <t>Ventas a valores constantes en supermercados. Variación interanual (%). Ciudad de Buenos Aires. Años 2001/julio de 2026</t>
+    <t>Ventas a valores constantes en supermercados. Variación interanual (%). Ciudad de Buenos Aires. Años 2001/agosto de 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#,##0_ ;[Red]\-#,##0\ "/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
@@ -1094,56 +1082,56 @@
     </xf>
   </cellXfs>
   <cellStyles count="50">
-    <cellStyle name="20% - Énfasis1 2" xfId="1"/>
-    <cellStyle name="20% - Énfasis2 2" xfId="2"/>
-    <cellStyle name="20% - Énfasis3 2" xfId="3"/>
-    <cellStyle name="20% - Énfasis4 2" xfId="4"/>
-    <cellStyle name="20% - Énfasis5 2" xfId="5"/>
-    <cellStyle name="20% - Énfasis6 2" xfId="6"/>
-    <cellStyle name="40% - Énfasis1 2" xfId="7"/>
-    <cellStyle name="40% - Énfasis2 2" xfId="8"/>
-    <cellStyle name="40% - Énfasis3 2" xfId="9"/>
-    <cellStyle name="40% - Énfasis4 2" xfId="10"/>
-    <cellStyle name="40% - Énfasis5 2" xfId="11"/>
-    <cellStyle name="40% - Énfasis6 2" xfId="12"/>
-    <cellStyle name="60% - Énfasis1 2" xfId="13"/>
-    <cellStyle name="60% - Énfasis2 2" xfId="14"/>
-    <cellStyle name="60% - Énfasis3 2" xfId="15"/>
-    <cellStyle name="60% - Énfasis4 2" xfId="16"/>
-    <cellStyle name="60% - Énfasis5 2" xfId="17"/>
-    <cellStyle name="60% - Énfasis6 2" xfId="18"/>
-    <cellStyle name="Buena 2" xfId="19"/>
-    <cellStyle name="Cálculo 2" xfId="20"/>
-    <cellStyle name="Celda de comprobación 2" xfId="21"/>
-    <cellStyle name="Celda vinculada 2" xfId="22"/>
-    <cellStyle name="Encabezado 4 2" xfId="23"/>
-    <cellStyle name="Énfasis1 2" xfId="24"/>
-    <cellStyle name="Énfasis2 2" xfId="25"/>
-    <cellStyle name="Énfasis3 2" xfId="26"/>
-    <cellStyle name="Énfasis4 2" xfId="27"/>
-    <cellStyle name="Énfasis5 2" xfId="28"/>
-    <cellStyle name="Énfasis6 2" xfId="29"/>
-    <cellStyle name="Entrada 2" xfId="30"/>
-    <cellStyle name="Euro" xfId="31"/>
-    <cellStyle name="Incorrecto 2" xfId="32"/>
-    <cellStyle name="mio" xfId="33"/>
-    <cellStyle name="Neutral 2" xfId="34"/>
+    <cellStyle name="20% - Énfasis1 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="20% - Énfasis2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="20% - Énfasis3 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="20% - Énfasis4 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="20% - Énfasis5 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="20% - Énfasis6 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="40% - Énfasis1 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="40% - Énfasis2 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="40% - Énfasis3 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="40% - Énfasis4 2" xfId="10" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="40% - Énfasis5 2" xfId="11" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="40% - Énfasis6 2" xfId="12" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="60% - Énfasis1 2" xfId="13" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="60% - Énfasis2 2" xfId="14" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="60% - Énfasis3 2" xfId="15" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="60% - Énfasis4 2" xfId="16" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="60% - Énfasis5 2" xfId="17" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="60% - Énfasis6 2" xfId="18" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="Buena 2" xfId="19" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="Cálculo 2" xfId="20" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="Celda de comprobación 2" xfId="21" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="Celda vinculada 2" xfId="22" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="Encabezado 4 2" xfId="23" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
+    <cellStyle name="Énfasis1 2" xfId="24" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
+    <cellStyle name="Énfasis2 2" xfId="25" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
+    <cellStyle name="Énfasis3 2" xfId="26" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
+    <cellStyle name="Énfasis4 2" xfId="27" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
+    <cellStyle name="Énfasis5 2" xfId="28" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
+    <cellStyle name="Énfasis6 2" xfId="29" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
+    <cellStyle name="Entrada 2" xfId="30" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
+    <cellStyle name="Euro" xfId="31" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
+    <cellStyle name="Incorrecto 2" xfId="32" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
+    <cellStyle name="mio" xfId="33" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
+    <cellStyle name="Neutral 2" xfId="34" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="35"/>
-    <cellStyle name="Normal 2 2" xfId="36"/>
-    <cellStyle name="Normal 2 3" xfId="49"/>
-    <cellStyle name="Normal 3" xfId="37"/>
-    <cellStyle name="Normal_Cuadro6comercio24" xfId="38"/>
-    <cellStyle name="Notas 2" xfId="39"/>
-    <cellStyle name="Pato" xfId="40"/>
-    <cellStyle name="Salida 2" xfId="41"/>
-    <cellStyle name="Texto de advertencia 2" xfId="42"/>
-    <cellStyle name="Texto explicativo 2" xfId="43"/>
-    <cellStyle name="Título 1 2" xfId="44"/>
-    <cellStyle name="Título 2 2" xfId="45"/>
-    <cellStyle name="Título 3 2" xfId="46"/>
-    <cellStyle name="Título 4" xfId="47"/>
-    <cellStyle name="Total 2" xfId="48"/>
+    <cellStyle name="Normal 2" xfId="35" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
+    <cellStyle name="Normal 2 2" xfId="36" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
+    <cellStyle name="Normal 2 3" xfId="49" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
+    <cellStyle name="Normal 3" xfId="37" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
+    <cellStyle name="Normal_Cuadro6comercio24" xfId="38" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
+    <cellStyle name="Notas 2" xfId="39" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
+    <cellStyle name="Pato" xfId="40" xr:uid="{00000000-0005-0000-0000-000029000000}"/>
+    <cellStyle name="Salida 2" xfId="41" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
+    <cellStyle name="Texto de advertencia 2" xfId="42" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
+    <cellStyle name="Texto explicativo 2" xfId="43" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
+    <cellStyle name="Título 1 2" xfId="44" xr:uid="{00000000-0005-0000-0000-00002D000000}"/>
+    <cellStyle name="Título 2 2" xfId="45" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
+    <cellStyle name="Título 3 2" xfId="46" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
+    <cellStyle name="Título 4" xfId="47" xr:uid="{00000000-0005-0000-0000-000030000000}"/>
+    <cellStyle name="Total 2" xfId="48" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1159,9 +1147,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1199,9 +1187,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1236,7 +1224,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1271,7 +1259,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1444,205 +1432,205 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J209"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J210"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="21" customWidth="1"/>
-    <col min="2" max="3" width="16.28515625" style="21" customWidth="1"/>
-    <col min="4" max="254" width="11.42578125" style="21"/>
-    <col min="255" max="255" width="13.85546875" style="21" customWidth="1"/>
-    <col min="256" max="256" width="12.85546875" style="21" customWidth="1"/>
-    <col min="257" max="510" width="11.42578125" style="21"/>
-    <col min="511" max="511" width="13.85546875" style="21" customWidth="1"/>
-    <col min="512" max="512" width="12.85546875" style="21" customWidth="1"/>
-    <col min="513" max="766" width="11.42578125" style="21"/>
-    <col min="767" max="767" width="13.85546875" style="21" customWidth="1"/>
-    <col min="768" max="768" width="12.85546875" style="21" customWidth="1"/>
-    <col min="769" max="1022" width="11.42578125" style="21"/>
-    <col min="1023" max="1023" width="13.85546875" style="21" customWidth="1"/>
-    <col min="1024" max="1024" width="12.85546875" style="21" customWidth="1"/>
-    <col min="1025" max="1278" width="11.42578125" style="21"/>
-    <col min="1279" max="1279" width="13.85546875" style="21" customWidth="1"/>
-    <col min="1280" max="1280" width="12.85546875" style="21" customWidth="1"/>
-    <col min="1281" max="1534" width="11.42578125" style="21"/>
-    <col min="1535" max="1535" width="13.85546875" style="21" customWidth="1"/>
-    <col min="1536" max="1536" width="12.85546875" style="21" customWidth="1"/>
-    <col min="1537" max="1790" width="11.42578125" style="21"/>
-    <col min="1791" max="1791" width="13.85546875" style="21" customWidth="1"/>
-    <col min="1792" max="1792" width="12.85546875" style="21" customWidth="1"/>
-    <col min="1793" max="2046" width="11.42578125" style="21"/>
-    <col min="2047" max="2047" width="13.85546875" style="21" customWidth="1"/>
-    <col min="2048" max="2048" width="12.85546875" style="21" customWidth="1"/>
-    <col min="2049" max="2302" width="11.42578125" style="21"/>
-    <col min="2303" max="2303" width="13.85546875" style="21" customWidth="1"/>
-    <col min="2304" max="2304" width="12.85546875" style="21" customWidth="1"/>
-    <col min="2305" max="2558" width="11.42578125" style="21"/>
-    <col min="2559" max="2559" width="13.85546875" style="21" customWidth="1"/>
-    <col min="2560" max="2560" width="12.85546875" style="21" customWidth="1"/>
-    <col min="2561" max="2814" width="11.42578125" style="21"/>
-    <col min="2815" max="2815" width="13.85546875" style="21" customWidth="1"/>
-    <col min="2816" max="2816" width="12.85546875" style="21" customWidth="1"/>
-    <col min="2817" max="3070" width="11.42578125" style="21"/>
-    <col min="3071" max="3071" width="13.85546875" style="21" customWidth="1"/>
-    <col min="3072" max="3072" width="12.85546875" style="21" customWidth="1"/>
-    <col min="3073" max="3326" width="11.42578125" style="21"/>
-    <col min="3327" max="3327" width="13.85546875" style="21" customWidth="1"/>
-    <col min="3328" max="3328" width="12.85546875" style="21" customWidth="1"/>
-    <col min="3329" max="3582" width="11.42578125" style="21"/>
-    <col min="3583" max="3583" width="13.85546875" style="21" customWidth="1"/>
-    <col min="3584" max="3584" width="12.85546875" style="21" customWidth="1"/>
-    <col min="3585" max="3838" width="11.42578125" style="21"/>
-    <col min="3839" max="3839" width="13.85546875" style="21" customWidth="1"/>
-    <col min="3840" max="3840" width="12.85546875" style="21" customWidth="1"/>
-    <col min="3841" max="4094" width="11.42578125" style="21"/>
-    <col min="4095" max="4095" width="13.85546875" style="21" customWidth="1"/>
-    <col min="4096" max="4096" width="12.85546875" style="21" customWidth="1"/>
-    <col min="4097" max="4350" width="11.42578125" style="21"/>
-    <col min="4351" max="4351" width="13.85546875" style="21" customWidth="1"/>
-    <col min="4352" max="4352" width="12.85546875" style="21" customWidth="1"/>
-    <col min="4353" max="4606" width="11.42578125" style="21"/>
-    <col min="4607" max="4607" width="13.85546875" style="21" customWidth="1"/>
-    <col min="4608" max="4608" width="12.85546875" style="21" customWidth="1"/>
-    <col min="4609" max="4862" width="11.42578125" style="21"/>
-    <col min="4863" max="4863" width="13.85546875" style="21" customWidth="1"/>
-    <col min="4864" max="4864" width="12.85546875" style="21" customWidth="1"/>
-    <col min="4865" max="5118" width="11.42578125" style="21"/>
-    <col min="5119" max="5119" width="13.85546875" style="21" customWidth="1"/>
-    <col min="5120" max="5120" width="12.85546875" style="21" customWidth="1"/>
-    <col min="5121" max="5374" width="11.42578125" style="21"/>
-    <col min="5375" max="5375" width="13.85546875" style="21" customWidth="1"/>
-    <col min="5376" max="5376" width="12.85546875" style="21" customWidth="1"/>
-    <col min="5377" max="5630" width="11.42578125" style="21"/>
-    <col min="5631" max="5631" width="13.85546875" style="21" customWidth="1"/>
-    <col min="5632" max="5632" width="12.85546875" style="21" customWidth="1"/>
-    <col min="5633" max="5886" width="11.42578125" style="21"/>
-    <col min="5887" max="5887" width="13.85546875" style="21" customWidth="1"/>
-    <col min="5888" max="5888" width="12.85546875" style="21" customWidth="1"/>
-    <col min="5889" max="6142" width="11.42578125" style="21"/>
-    <col min="6143" max="6143" width="13.85546875" style="21" customWidth="1"/>
-    <col min="6144" max="6144" width="12.85546875" style="21" customWidth="1"/>
-    <col min="6145" max="6398" width="11.42578125" style="21"/>
-    <col min="6399" max="6399" width="13.85546875" style="21" customWidth="1"/>
-    <col min="6400" max="6400" width="12.85546875" style="21" customWidth="1"/>
-    <col min="6401" max="6654" width="11.42578125" style="21"/>
-    <col min="6655" max="6655" width="13.85546875" style="21" customWidth="1"/>
-    <col min="6656" max="6656" width="12.85546875" style="21" customWidth="1"/>
-    <col min="6657" max="6910" width="11.42578125" style="21"/>
-    <col min="6911" max="6911" width="13.85546875" style="21" customWidth="1"/>
-    <col min="6912" max="6912" width="12.85546875" style="21" customWidth="1"/>
-    <col min="6913" max="7166" width="11.42578125" style="21"/>
-    <col min="7167" max="7167" width="13.85546875" style="21" customWidth="1"/>
-    <col min="7168" max="7168" width="12.85546875" style="21" customWidth="1"/>
-    <col min="7169" max="7422" width="11.42578125" style="21"/>
-    <col min="7423" max="7423" width="13.85546875" style="21" customWidth="1"/>
-    <col min="7424" max="7424" width="12.85546875" style="21" customWidth="1"/>
-    <col min="7425" max="7678" width="11.42578125" style="21"/>
-    <col min="7679" max="7679" width="13.85546875" style="21" customWidth="1"/>
-    <col min="7680" max="7680" width="12.85546875" style="21" customWidth="1"/>
-    <col min="7681" max="7934" width="11.42578125" style="21"/>
-    <col min="7935" max="7935" width="13.85546875" style="21" customWidth="1"/>
-    <col min="7936" max="7936" width="12.85546875" style="21" customWidth="1"/>
-    <col min="7937" max="8190" width="11.42578125" style="21"/>
-    <col min="8191" max="8191" width="13.85546875" style="21" customWidth="1"/>
-    <col min="8192" max="8192" width="12.85546875" style="21" customWidth="1"/>
-    <col min="8193" max="8446" width="11.42578125" style="21"/>
-    <col min="8447" max="8447" width="13.85546875" style="21" customWidth="1"/>
-    <col min="8448" max="8448" width="12.85546875" style="21" customWidth="1"/>
-    <col min="8449" max="8702" width="11.42578125" style="21"/>
-    <col min="8703" max="8703" width="13.85546875" style="21" customWidth="1"/>
-    <col min="8704" max="8704" width="12.85546875" style="21" customWidth="1"/>
-    <col min="8705" max="8958" width="11.42578125" style="21"/>
-    <col min="8959" max="8959" width="13.85546875" style="21" customWidth="1"/>
-    <col min="8960" max="8960" width="12.85546875" style="21" customWidth="1"/>
-    <col min="8961" max="9214" width="11.42578125" style="21"/>
-    <col min="9215" max="9215" width="13.85546875" style="21" customWidth="1"/>
-    <col min="9216" max="9216" width="12.85546875" style="21" customWidth="1"/>
-    <col min="9217" max="9470" width="11.42578125" style="21"/>
-    <col min="9471" max="9471" width="13.85546875" style="21" customWidth="1"/>
-    <col min="9472" max="9472" width="12.85546875" style="21" customWidth="1"/>
-    <col min="9473" max="9726" width="11.42578125" style="21"/>
-    <col min="9727" max="9727" width="13.85546875" style="21" customWidth="1"/>
-    <col min="9728" max="9728" width="12.85546875" style="21" customWidth="1"/>
-    <col min="9729" max="9982" width="11.42578125" style="21"/>
-    <col min="9983" max="9983" width="13.85546875" style="21" customWidth="1"/>
-    <col min="9984" max="9984" width="12.85546875" style="21" customWidth="1"/>
-    <col min="9985" max="10238" width="11.42578125" style="21"/>
-    <col min="10239" max="10239" width="13.85546875" style="21" customWidth="1"/>
-    <col min="10240" max="10240" width="12.85546875" style="21" customWidth="1"/>
-    <col min="10241" max="10494" width="11.42578125" style="21"/>
-    <col min="10495" max="10495" width="13.85546875" style="21" customWidth="1"/>
-    <col min="10496" max="10496" width="12.85546875" style="21" customWidth="1"/>
-    <col min="10497" max="10750" width="11.42578125" style="21"/>
-    <col min="10751" max="10751" width="13.85546875" style="21" customWidth="1"/>
-    <col min="10752" max="10752" width="12.85546875" style="21" customWidth="1"/>
-    <col min="10753" max="11006" width="11.42578125" style="21"/>
-    <col min="11007" max="11007" width="13.85546875" style="21" customWidth="1"/>
-    <col min="11008" max="11008" width="12.85546875" style="21" customWidth="1"/>
-    <col min="11009" max="11262" width="11.42578125" style="21"/>
-    <col min="11263" max="11263" width="13.85546875" style="21" customWidth="1"/>
-    <col min="11264" max="11264" width="12.85546875" style="21" customWidth="1"/>
-    <col min="11265" max="11518" width="11.42578125" style="21"/>
-    <col min="11519" max="11519" width="13.85546875" style="21" customWidth="1"/>
-    <col min="11520" max="11520" width="12.85546875" style="21" customWidth="1"/>
-    <col min="11521" max="11774" width="11.42578125" style="21"/>
-    <col min="11775" max="11775" width="13.85546875" style="21" customWidth="1"/>
-    <col min="11776" max="11776" width="12.85546875" style="21" customWidth="1"/>
-    <col min="11777" max="12030" width="11.42578125" style="21"/>
-    <col min="12031" max="12031" width="13.85546875" style="21" customWidth="1"/>
-    <col min="12032" max="12032" width="12.85546875" style="21" customWidth="1"/>
-    <col min="12033" max="12286" width="11.42578125" style="21"/>
-    <col min="12287" max="12287" width="13.85546875" style="21" customWidth="1"/>
-    <col min="12288" max="12288" width="12.85546875" style="21" customWidth="1"/>
-    <col min="12289" max="12542" width="11.42578125" style="21"/>
-    <col min="12543" max="12543" width="13.85546875" style="21" customWidth="1"/>
-    <col min="12544" max="12544" width="12.85546875" style="21" customWidth="1"/>
-    <col min="12545" max="12798" width="11.42578125" style="21"/>
-    <col min="12799" max="12799" width="13.85546875" style="21" customWidth="1"/>
-    <col min="12800" max="12800" width="12.85546875" style="21" customWidth="1"/>
-    <col min="12801" max="13054" width="11.42578125" style="21"/>
-    <col min="13055" max="13055" width="13.85546875" style="21" customWidth="1"/>
-    <col min="13056" max="13056" width="12.85546875" style="21" customWidth="1"/>
-    <col min="13057" max="13310" width="11.42578125" style="21"/>
-    <col min="13311" max="13311" width="13.85546875" style="21" customWidth="1"/>
-    <col min="13312" max="13312" width="12.85546875" style="21" customWidth="1"/>
-    <col min="13313" max="13566" width="11.42578125" style="21"/>
-    <col min="13567" max="13567" width="13.85546875" style="21" customWidth="1"/>
-    <col min="13568" max="13568" width="12.85546875" style="21" customWidth="1"/>
-    <col min="13569" max="13822" width="11.42578125" style="21"/>
-    <col min="13823" max="13823" width="13.85546875" style="21" customWidth="1"/>
-    <col min="13824" max="13824" width="12.85546875" style="21" customWidth="1"/>
-    <col min="13825" max="14078" width="11.42578125" style="21"/>
-    <col min="14079" max="14079" width="13.85546875" style="21" customWidth="1"/>
-    <col min="14080" max="14080" width="12.85546875" style="21" customWidth="1"/>
-    <col min="14081" max="14334" width="11.42578125" style="21"/>
-    <col min="14335" max="14335" width="13.85546875" style="21" customWidth="1"/>
-    <col min="14336" max="14336" width="12.85546875" style="21" customWidth="1"/>
-    <col min="14337" max="14590" width="11.42578125" style="21"/>
-    <col min="14591" max="14591" width="13.85546875" style="21" customWidth="1"/>
-    <col min="14592" max="14592" width="12.85546875" style="21" customWidth="1"/>
-    <col min="14593" max="14846" width="11.42578125" style="21"/>
-    <col min="14847" max="14847" width="13.85546875" style="21" customWidth="1"/>
-    <col min="14848" max="14848" width="12.85546875" style="21" customWidth="1"/>
-    <col min="14849" max="15102" width="11.42578125" style="21"/>
-    <col min="15103" max="15103" width="13.85546875" style="21" customWidth="1"/>
-    <col min="15104" max="15104" width="12.85546875" style="21" customWidth="1"/>
-    <col min="15105" max="15358" width="11.42578125" style="21"/>
-    <col min="15359" max="15359" width="13.85546875" style="21" customWidth="1"/>
-    <col min="15360" max="15360" width="12.85546875" style="21" customWidth="1"/>
-    <col min="15361" max="15614" width="11.42578125" style="21"/>
-    <col min="15615" max="15615" width="13.85546875" style="21" customWidth="1"/>
-    <col min="15616" max="15616" width="12.85546875" style="21" customWidth="1"/>
-    <col min="15617" max="15870" width="11.42578125" style="21"/>
-    <col min="15871" max="15871" width="13.85546875" style="21" customWidth="1"/>
-    <col min="15872" max="15872" width="12.85546875" style="21" customWidth="1"/>
-    <col min="15873" max="16126" width="11.42578125" style="21"/>
-    <col min="16127" max="16127" width="13.85546875" style="21" customWidth="1"/>
-    <col min="16128" max="16128" width="12.85546875" style="21" customWidth="1"/>
-    <col min="16129" max="16384" width="11.42578125" style="21"/>
+    <col min="1" max="1" width="13.5546875" style="21" customWidth="1"/>
+    <col min="2" max="3" width="16.33203125" style="21" customWidth="1"/>
+    <col min="4" max="254" width="11.44140625" style="21"/>
+    <col min="255" max="255" width="13.88671875" style="21" customWidth="1"/>
+    <col min="256" max="256" width="12.88671875" style="21" customWidth="1"/>
+    <col min="257" max="510" width="11.44140625" style="21"/>
+    <col min="511" max="511" width="13.88671875" style="21" customWidth="1"/>
+    <col min="512" max="512" width="12.88671875" style="21" customWidth="1"/>
+    <col min="513" max="766" width="11.44140625" style="21"/>
+    <col min="767" max="767" width="13.88671875" style="21" customWidth="1"/>
+    <col min="768" max="768" width="12.88671875" style="21" customWidth="1"/>
+    <col min="769" max="1022" width="11.44140625" style="21"/>
+    <col min="1023" max="1023" width="13.88671875" style="21" customWidth="1"/>
+    <col min="1024" max="1024" width="12.88671875" style="21" customWidth="1"/>
+    <col min="1025" max="1278" width="11.44140625" style="21"/>
+    <col min="1279" max="1279" width="13.88671875" style="21" customWidth="1"/>
+    <col min="1280" max="1280" width="12.88671875" style="21" customWidth="1"/>
+    <col min="1281" max="1534" width="11.44140625" style="21"/>
+    <col min="1535" max="1535" width="13.88671875" style="21" customWidth="1"/>
+    <col min="1536" max="1536" width="12.88671875" style="21" customWidth="1"/>
+    <col min="1537" max="1790" width="11.44140625" style="21"/>
+    <col min="1791" max="1791" width="13.88671875" style="21" customWidth="1"/>
+    <col min="1792" max="1792" width="12.88671875" style="21" customWidth="1"/>
+    <col min="1793" max="2046" width="11.44140625" style="21"/>
+    <col min="2047" max="2047" width="13.88671875" style="21" customWidth="1"/>
+    <col min="2048" max="2048" width="12.88671875" style="21" customWidth="1"/>
+    <col min="2049" max="2302" width="11.44140625" style="21"/>
+    <col min="2303" max="2303" width="13.88671875" style="21" customWidth="1"/>
+    <col min="2304" max="2304" width="12.88671875" style="21" customWidth="1"/>
+    <col min="2305" max="2558" width="11.44140625" style="21"/>
+    <col min="2559" max="2559" width="13.88671875" style="21" customWidth="1"/>
+    <col min="2560" max="2560" width="12.88671875" style="21" customWidth="1"/>
+    <col min="2561" max="2814" width="11.44140625" style="21"/>
+    <col min="2815" max="2815" width="13.88671875" style="21" customWidth="1"/>
+    <col min="2816" max="2816" width="12.88671875" style="21" customWidth="1"/>
+    <col min="2817" max="3070" width="11.44140625" style="21"/>
+    <col min="3071" max="3071" width="13.88671875" style="21" customWidth="1"/>
+    <col min="3072" max="3072" width="12.88671875" style="21" customWidth="1"/>
+    <col min="3073" max="3326" width="11.44140625" style="21"/>
+    <col min="3327" max="3327" width="13.88671875" style="21" customWidth="1"/>
+    <col min="3328" max="3328" width="12.88671875" style="21" customWidth="1"/>
+    <col min="3329" max="3582" width="11.44140625" style="21"/>
+    <col min="3583" max="3583" width="13.88671875" style="21" customWidth="1"/>
+    <col min="3584" max="3584" width="12.88671875" style="21" customWidth="1"/>
+    <col min="3585" max="3838" width="11.44140625" style="21"/>
+    <col min="3839" max="3839" width="13.88671875" style="21" customWidth="1"/>
+    <col min="3840" max="3840" width="12.88671875" style="21" customWidth="1"/>
+    <col min="3841" max="4094" width="11.44140625" style="21"/>
+    <col min="4095" max="4095" width="13.88671875" style="21" customWidth="1"/>
+    <col min="4096" max="4096" width="12.88671875" style="21" customWidth="1"/>
+    <col min="4097" max="4350" width="11.44140625" style="21"/>
+    <col min="4351" max="4351" width="13.88671875" style="21" customWidth="1"/>
+    <col min="4352" max="4352" width="12.88671875" style="21" customWidth="1"/>
+    <col min="4353" max="4606" width="11.44140625" style="21"/>
+    <col min="4607" max="4607" width="13.88671875" style="21" customWidth="1"/>
+    <col min="4608" max="4608" width="12.88671875" style="21" customWidth="1"/>
+    <col min="4609" max="4862" width="11.44140625" style="21"/>
+    <col min="4863" max="4863" width="13.88671875" style="21" customWidth="1"/>
+    <col min="4864" max="4864" width="12.88671875" style="21" customWidth="1"/>
+    <col min="4865" max="5118" width="11.44140625" style="21"/>
+    <col min="5119" max="5119" width="13.88671875" style="21" customWidth="1"/>
+    <col min="5120" max="5120" width="12.88671875" style="21" customWidth="1"/>
+    <col min="5121" max="5374" width="11.44140625" style="21"/>
+    <col min="5375" max="5375" width="13.88671875" style="21" customWidth="1"/>
+    <col min="5376" max="5376" width="12.88671875" style="21" customWidth="1"/>
+    <col min="5377" max="5630" width="11.44140625" style="21"/>
+    <col min="5631" max="5631" width="13.88671875" style="21" customWidth="1"/>
+    <col min="5632" max="5632" width="12.88671875" style="21" customWidth="1"/>
+    <col min="5633" max="5886" width="11.44140625" style="21"/>
+    <col min="5887" max="5887" width="13.88671875" style="21" customWidth="1"/>
+    <col min="5888" max="5888" width="12.88671875" style="21" customWidth="1"/>
+    <col min="5889" max="6142" width="11.44140625" style="21"/>
+    <col min="6143" max="6143" width="13.88671875" style="21" customWidth="1"/>
+    <col min="6144" max="6144" width="12.88671875" style="21" customWidth="1"/>
+    <col min="6145" max="6398" width="11.44140625" style="21"/>
+    <col min="6399" max="6399" width="13.88671875" style="21" customWidth="1"/>
+    <col min="6400" max="6400" width="12.88671875" style="21" customWidth="1"/>
+    <col min="6401" max="6654" width="11.44140625" style="21"/>
+    <col min="6655" max="6655" width="13.88671875" style="21" customWidth="1"/>
+    <col min="6656" max="6656" width="12.88671875" style="21" customWidth="1"/>
+    <col min="6657" max="6910" width="11.44140625" style="21"/>
+    <col min="6911" max="6911" width="13.88671875" style="21" customWidth="1"/>
+    <col min="6912" max="6912" width="12.88671875" style="21" customWidth="1"/>
+    <col min="6913" max="7166" width="11.44140625" style="21"/>
+    <col min="7167" max="7167" width="13.88671875" style="21" customWidth="1"/>
+    <col min="7168" max="7168" width="12.88671875" style="21" customWidth="1"/>
+    <col min="7169" max="7422" width="11.44140625" style="21"/>
+    <col min="7423" max="7423" width="13.88671875" style="21" customWidth="1"/>
+    <col min="7424" max="7424" width="12.88671875" style="21" customWidth="1"/>
+    <col min="7425" max="7678" width="11.44140625" style="21"/>
+    <col min="7679" max="7679" width="13.88671875" style="21" customWidth="1"/>
+    <col min="7680" max="7680" width="12.88671875" style="21" customWidth="1"/>
+    <col min="7681" max="7934" width="11.44140625" style="21"/>
+    <col min="7935" max="7935" width="13.88671875" style="21" customWidth="1"/>
+    <col min="7936" max="7936" width="12.88671875" style="21" customWidth="1"/>
+    <col min="7937" max="8190" width="11.44140625" style="21"/>
+    <col min="8191" max="8191" width="13.88671875" style="21" customWidth="1"/>
+    <col min="8192" max="8192" width="12.88671875" style="21" customWidth="1"/>
+    <col min="8193" max="8446" width="11.44140625" style="21"/>
+    <col min="8447" max="8447" width="13.88671875" style="21" customWidth="1"/>
+    <col min="8448" max="8448" width="12.88671875" style="21" customWidth="1"/>
+    <col min="8449" max="8702" width="11.44140625" style="21"/>
+    <col min="8703" max="8703" width="13.88671875" style="21" customWidth="1"/>
+    <col min="8704" max="8704" width="12.88671875" style="21" customWidth="1"/>
+    <col min="8705" max="8958" width="11.44140625" style="21"/>
+    <col min="8959" max="8959" width="13.88671875" style="21" customWidth="1"/>
+    <col min="8960" max="8960" width="12.88671875" style="21" customWidth="1"/>
+    <col min="8961" max="9214" width="11.44140625" style="21"/>
+    <col min="9215" max="9215" width="13.88671875" style="21" customWidth="1"/>
+    <col min="9216" max="9216" width="12.88671875" style="21" customWidth="1"/>
+    <col min="9217" max="9470" width="11.44140625" style="21"/>
+    <col min="9471" max="9471" width="13.88671875" style="21" customWidth="1"/>
+    <col min="9472" max="9472" width="12.88671875" style="21" customWidth="1"/>
+    <col min="9473" max="9726" width="11.44140625" style="21"/>
+    <col min="9727" max="9727" width="13.88671875" style="21" customWidth="1"/>
+    <col min="9728" max="9728" width="12.88671875" style="21" customWidth="1"/>
+    <col min="9729" max="9982" width="11.44140625" style="21"/>
+    <col min="9983" max="9983" width="13.88671875" style="21" customWidth="1"/>
+    <col min="9984" max="9984" width="12.88671875" style="21" customWidth="1"/>
+    <col min="9985" max="10238" width="11.44140625" style="21"/>
+    <col min="10239" max="10239" width="13.88671875" style="21" customWidth="1"/>
+    <col min="10240" max="10240" width="12.88671875" style="21" customWidth="1"/>
+    <col min="10241" max="10494" width="11.44140625" style="21"/>
+    <col min="10495" max="10495" width="13.88671875" style="21" customWidth="1"/>
+    <col min="10496" max="10496" width="12.88671875" style="21" customWidth="1"/>
+    <col min="10497" max="10750" width="11.44140625" style="21"/>
+    <col min="10751" max="10751" width="13.88671875" style="21" customWidth="1"/>
+    <col min="10752" max="10752" width="12.88671875" style="21" customWidth="1"/>
+    <col min="10753" max="11006" width="11.44140625" style="21"/>
+    <col min="11007" max="11007" width="13.88671875" style="21" customWidth="1"/>
+    <col min="11008" max="11008" width="12.88671875" style="21" customWidth="1"/>
+    <col min="11009" max="11262" width="11.44140625" style="21"/>
+    <col min="11263" max="11263" width="13.88671875" style="21" customWidth="1"/>
+    <col min="11264" max="11264" width="12.88671875" style="21" customWidth="1"/>
+    <col min="11265" max="11518" width="11.44140625" style="21"/>
+    <col min="11519" max="11519" width="13.88671875" style="21" customWidth="1"/>
+    <col min="11520" max="11520" width="12.88671875" style="21" customWidth="1"/>
+    <col min="11521" max="11774" width="11.44140625" style="21"/>
+    <col min="11775" max="11775" width="13.88671875" style="21" customWidth="1"/>
+    <col min="11776" max="11776" width="12.88671875" style="21" customWidth="1"/>
+    <col min="11777" max="12030" width="11.44140625" style="21"/>
+    <col min="12031" max="12031" width="13.88671875" style="21" customWidth="1"/>
+    <col min="12032" max="12032" width="12.88671875" style="21" customWidth="1"/>
+    <col min="12033" max="12286" width="11.44140625" style="21"/>
+    <col min="12287" max="12287" width="13.88671875" style="21" customWidth="1"/>
+    <col min="12288" max="12288" width="12.88671875" style="21" customWidth="1"/>
+    <col min="12289" max="12542" width="11.44140625" style="21"/>
+    <col min="12543" max="12543" width="13.88671875" style="21" customWidth="1"/>
+    <col min="12544" max="12544" width="12.88671875" style="21" customWidth="1"/>
+    <col min="12545" max="12798" width="11.44140625" style="21"/>
+    <col min="12799" max="12799" width="13.88671875" style="21" customWidth="1"/>
+    <col min="12800" max="12800" width="12.88671875" style="21" customWidth="1"/>
+    <col min="12801" max="13054" width="11.44140625" style="21"/>
+    <col min="13055" max="13055" width="13.88671875" style="21" customWidth="1"/>
+    <col min="13056" max="13056" width="12.88671875" style="21" customWidth="1"/>
+    <col min="13057" max="13310" width="11.44140625" style="21"/>
+    <col min="13311" max="13311" width="13.88671875" style="21" customWidth="1"/>
+    <col min="13312" max="13312" width="12.88671875" style="21" customWidth="1"/>
+    <col min="13313" max="13566" width="11.44140625" style="21"/>
+    <col min="13567" max="13567" width="13.88671875" style="21" customWidth="1"/>
+    <col min="13568" max="13568" width="12.88671875" style="21" customWidth="1"/>
+    <col min="13569" max="13822" width="11.44140625" style="21"/>
+    <col min="13823" max="13823" width="13.88671875" style="21" customWidth="1"/>
+    <col min="13824" max="13824" width="12.88671875" style="21" customWidth="1"/>
+    <col min="13825" max="14078" width="11.44140625" style="21"/>
+    <col min="14079" max="14079" width="13.88671875" style="21" customWidth="1"/>
+    <col min="14080" max="14080" width="12.88671875" style="21" customWidth="1"/>
+    <col min="14081" max="14334" width="11.44140625" style="21"/>
+    <col min="14335" max="14335" width="13.88671875" style="21" customWidth="1"/>
+    <col min="14336" max="14336" width="12.88671875" style="21" customWidth="1"/>
+    <col min="14337" max="14590" width="11.44140625" style="21"/>
+    <col min="14591" max="14591" width="13.88671875" style="21" customWidth="1"/>
+    <col min="14592" max="14592" width="12.88671875" style="21" customWidth="1"/>
+    <col min="14593" max="14846" width="11.44140625" style="21"/>
+    <col min="14847" max="14847" width="13.88671875" style="21" customWidth="1"/>
+    <col min="14848" max="14848" width="12.88671875" style="21" customWidth="1"/>
+    <col min="14849" max="15102" width="11.44140625" style="21"/>
+    <col min="15103" max="15103" width="13.88671875" style="21" customWidth="1"/>
+    <col min="15104" max="15104" width="12.88671875" style="21" customWidth="1"/>
+    <col min="15105" max="15358" width="11.44140625" style="21"/>
+    <col min="15359" max="15359" width="13.88671875" style="21" customWidth="1"/>
+    <col min="15360" max="15360" width="12.88671875" style="21" customWidth="1"/>
+    <col min="15361" max="15614" width="11.44140625" style="21"/>
+    <col min="15615" max="15615" width="13.88671875" style="21" customWidth="1"/>
+    <col min="15616" max="15616" width="12.88671875" style="21" customWidth="1"/>
+    <col min="15617" max="15870" width="11.44140625" style="21"/>
+    <col min="15871" max="15871" width="13.88671875" style="21" customWidth="1"/>
+    <col min="15872" max="15872" width="12.88671875" style="21" customWidth="1"/>
+    <col min="15873" max="16126" width="11.44140625" style="21"/>
+    <col min="16127" max="16127" width="13.88671875" style="21" customWidth="1"/>
+    <col min="16128" max="16128" width="12.88671875" style="21" customWidth="1"/>
+    <col min="16129" max="16384" width="11.44140625" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="38" t="s">
         <v>65</v>
       </c>
@@ -1677,7 +1665,7 @@
       </c>
       <c r="C4" s="43"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="12" x14ac:dyDescent="0.25">
       <c r="A5" s="20">
         <v>2001</v>
       </c>
@@ -1688,7 +1676,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="12" x14ac:dyDescent="0.25">
       <c r="A6" s="20">
         <v>2002</v>
       </c>
@@ -1699,7 +1687,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="12" x14ac:dyDescent="0.25">
       <c r="A7" s="20">
         <v>2003</v>
       </c>
@@ -1710,7 +1698,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="12" x14ac:dyDescent="0.25">
       <c r="A8" s="20">
         <v>2004</v>
       </c>
@@ -1721,7 +1709,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="12" x14ac:dyDescent="0.25">
       <c r="A9" s="20">
         <v>2005</v>
       </c>
@@ -1732,7 +1720,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="12" x14ac:dyDescent="0.25">
       <c r="A10" s="20">
         <v>2006</v>
       </c>
@@ -1743,7 +1731,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="12" x14ac:dyDescent="0.25">
       <c r="A11" s="20">
         <v>2007</v>
       </c>
@@ -1754,7 +1742,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="12" x14ac:dyDescent="0.25">
       <c r="A12" s="20">
         <v>2008</v>
       </c>
@@ -1765,7 +1753,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ht="12" x14ac:dyDescent="0.25">
       <c r="A13" s="20">
         <v>2009</v>
       </c>
@@ -1776,7 +1764,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ht="12" x14ac:dyDescent="0.25">
       <c r="A14" s="20">
         <v>2010</v>
       </c>
@@ -1787,7 +1775,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" ht="12" x14ac:dyDescent="0.25">
       <c r="A15" s="20">
         <v>2011</v>
       </c>
@@ -1798,7 +1786,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ht="12" x14ac:dyDescent="0.25">
       <c r="A16" s="20">
         <v>2012</v>
       </c>
@@ -1941,7 +1929,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A29" s="20">
         <v>2013</v>
       </c>
@@ -2084,7 +2072,7 @@
         <v>2.9693301873396694</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A42" s="20">
         <v>2014</v>
       </c>
@@ -2227,7 +2215,7 @@
         <v>-1.0058318246483733</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A55" s="20">
         <v>2015</v>
       </c>
@@ -2370,7 +2358,7 @@
         <v>-3.5332268244495535</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A68" s="20">
         <v>2016</v>
       </c>
@@ -2513,7 +2501,7 @@
         <v>-5.2537378015719005</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A81" s="20">
         <v>2017</v>
       </c>
@@ -2656,7 +2644,7 @@
         <v>-1.7551934757647381</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A94" s="20">
         <v>2018</v>
       </c>
@@ -2799,7 +2787,7 @@
         <v>-8.4233367249454858</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6" ht="12" x14ac:dyDescent="0.25">
       <c r="A107" s="20">
         <v>2019</v>
       </c>
@@ -2954,7 +2942,7 @@
       </c>
       <c r="F119" s="26"/>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" ht="12" x14ac:dyDescent="0.25">
       <c r="A120" s="20">
         <v>2020</v>
       </c>
@@ -3097,7 +3085,7 @@
         <v>-0.32084083611805259</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A133" s="20">
         <v>2021</v>
       </c>
@@ -3240,7 +3228,7 @@
         <v>5.4979873117792399</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A146" s="20">
         <v>2022</v>
       </c>
@@ -3383,7 +3371,7 @@
         <v>-2.1042775171962291</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A159" s="20">
         <v>2023</v>
       </c>
@@ -3526,7 +3514,7 @@
         <v>-0.89020151586457485</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A172" s="20" t="s">
         <v>62</v>
       </c>
@@ -3616,7 +3604,7 @@
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A180" s="21" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B180" s="30">
         <v>-3.1186552143895985</v>
@@ -3669,7 +3657,7 @@
         <v>-5.8219434853522323</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A185" s="20" t="s">
         <v>64</v>
       </c>
@@ -3812,7 +3800,7 @@
         <v>2.2370658176845692</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:10" ht="12" x14ac:dyDescent="0.25">
       <c r="A198" s="20">
         <v>2026</v>
       </c>
@@ -3896,46 +3884,57 @@
         <v>0.74044303817519808</v>
       </c>
     </row>
-    <row r="206" spans="1:10" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A206" s="36" t="s">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A206" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B206" s="30">
+        <v>-0.14635898707338058</v>
+      </c>
+      <c r="C206" s="30">
+        <v>-0.36465894228472351</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A207" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="B206" s="36"/>
-      <c r="C206" s="36"/>
-    </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A207" s="37" t="s">
+      <c r="B207" s="36"/>
+      <c r="C207" s="36"/>
+    </row>
+    <row r="208" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A208" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="B207" s="37"/>
-      <c r="C207" s="37"/>
-      <c r="D207" s="29"/>
-      <c r="E207" s="29"/>
-      <c r="F207" s="29"/>
-      <c r="H207" s="29"/>
-      <c r="I207" s="29"/>
-      <c r="J207" s="29"/>
-    </row>
-    <row r="208" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A208" s="35" t="s">
+      <c r="B208" s="37"/>
+      <c r="C208" s="37"/>
+      <c r="D208" s="29"/>
+      <c r="E208" s="29"/>
+      <c r="F208" s="29"/>
+      <c r="H208" s="29"/>
+      <c r="I208" s="29"/>
+      <c r="J208" s="29"/>
+    </row>
+    <row r="209" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A209" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="B208" s="35"/>
-      <c r="C208" s="35"/>
-    </row>
-    <row r="209" spans="1:3" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A209" s="34" t="s">
+      <c r="B209" s="35"/>
+      <c r="C209" s="35"/>
+    </row>
+    <row r="210" spans="1:3" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A210" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="B209" s="34"/>
-      <c r="C209" s="34"/>
+      <c r="B210" s="34"/>
+      <c r="C210" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A210:C210"/>
     <mergeCell ref="A209:C209"/>
+    <mergeCell ref="A207:C207"/>
     <mergeCell ref="A208:C208"/>
-    <mergeCell ref="A206:C206"/>
-    <mergeCell ref="A207:C207"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:C2"/>
@@ -3949,23 +3948,23 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="47.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="29.140625" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="11.42578125" style="1"/>
+    <col min="1" max="1" width="47.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="29.109375" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44" t="s">
         <v>33</v>
       </c>
       <c r="B1" s="45"/>
     </row>
-    <row r="2" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>34</v>
       </c>
@@ -3973,7 +3972,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -3981,7 +3980,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>36</v>
       </c>
@@ -3989,7 +3988,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>37</v>
       </c>
@@ -3997,7 +3996,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>39</v>
       </c>
@@ -4006,7 +4005,7 @@
       </c>
       <c r="D6" s="10"/>
     </row>
-    <row r="7" spans="1:4" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
         <v>40</v>
       </c>
@@ -4014,7 +4013,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>41</v>
       </c>
@@ -4022,7 +4021,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>42</v>
       </c>
@@ -4031,7 +4030,7 @@
       </c>
       <c r="C9" s="19"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>43</v>
       </c>
@@ -4039,7 +4038,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="15" t="s">
         <v>44</v>
       </c>
@@ -4047,7 +4046,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>45</v>
       </c>
@@ -4055,7 +4054,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>46</v>
       </c>
@@ -4063,7 +4062,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>47</v>
       </c>
@@ -4071,7 +4070,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="73.150000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="73.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="17" t="s">
         <v>48</v>
       </c>
